--- a/Graph.xlsx
+++ b/Graph.xlsx
@@ -8,20 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ResearchProject\Sorowar Sir\Causes of Deaths\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED92DE60-6090-41A4-9604-EB6ABC9269ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{780F94BB-A09A-4C3E-907D-2F971571796C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{D59E1812-00E2-46C2-B4ED-CEBFB390F202}"/>
   </bookViews>
   <sheets>
     <sheet name="Graph" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$1:$B$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="60">
   <si>
     <t>Jan</t>
   </si>
@@ -192,6 +196,15 @@
   </si>
   <si>
     <t>Unknown Cause</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Causes of death</t>
+  </si>
+  <si>
+    <t>Numbers</t>
   </si>
 </sst>
 </file>
@@ -752,6 +765,625 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Numbers</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$A$2:$A$36</c:f>
+              <c:strCache>
+                <c:ptCount val="35"/>
+                <c:pt idx="0">
+                  <c:v>Rail accident</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Cold</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Injury</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Fire Accident</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Breast Cancer</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Ulcer</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Electric accident</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Blood Cancer</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Brain tumor</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Cardiac Arrest</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Train Accident</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Anemia</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Covid-19</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Tumer</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Tuberculosis</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Drowning</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Diarrhea</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Neonatal death</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Lung Failure</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Road Accident</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Jaundice</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Lung Cancer</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>Maternal Death</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>Fever</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>Diabetes</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>Paralysis</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>Heart Disease</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>Other</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>Kidney Failure</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>Asthma</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>Other Accident</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>Pneumonia</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>Cancer</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>Stroke</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>Unknown</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$B$2:$B$36</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="35"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>63</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>139</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>148</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>153</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>159</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>231</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>248</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>251</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>282</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>297</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>346</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>537</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2833</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>4138</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5251-4BBC-9417-1BAD1317802A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="678678936"/>
+        <c:axId val="678681096"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="678678936"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Causes of Death</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="678681096"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="678681096"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Disease Counts</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="678678936"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
@@ -830,6 +1462,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-D148-48F2-9093-63FAAA0C380F}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -845,6 +1482,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-D148-48F2-9093-63FAAA0C380F}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -1025,7 +1667,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1116,6 +1758,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-FE39-45FB-A4CF-4635961CE490}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -1131,6 +1778,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-FE39-45FB-A4CF-4635961CE490}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -1146,6 +1798,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-FE39-45FB-A4CF-4635961CE490}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -1161,6 +1818,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-FE39-45FB-A4CF-4635961CE490}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -1176,6 +1838,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-FE39-45FB-A4CF-4635961CE490}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -1191,6 +1858,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-FE39-45FB-A4CF-4635961CE490}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -1482,8 +2154,48 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -1540,7 +2252,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -1591,13 +2303,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -1608,19 +2313,12 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="25400">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -1658,6 +2356,523 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
@@ -2001,7 +3216,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -2525,15 +3740,56 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1200150</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>57149</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D6F7333-A335-5D75-0EB4-A3EBE2C0FA17}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2894,10 +4150,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC37967C-A1B0-4A26-B59C-005374D51796}">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -2934,8 +4190,11 @@
       <c r="M1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2011</v>
       </c>
@@ -2975,8 +4234,12 @@
       <c r="M2">
         <v>90</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N2">
+        <f>SUM(B2:M2)</f>
+        <v>815</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2012</v>
       </c>
@@ -3016,8 +4279,12 @@
       <c r="M3">
         <v>69</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N3">
+        <f t="shared" ref="N3:N12" si="0">SUM(B3:M3)</f>
+        <v>763</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2013</v>
       </c>
@@ -3057,8 +4324,12 @@
       <c r="M4">
         <v>57</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N4">
+        <f t="shared" si="0"/>
+        <v>754</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2014</v>
       </c>
@@ -3098,8 +4369,12 @@
       <c r="M5">
         <v>64</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N5">
+        <f t="shared" si="0"/>
+        <v>845</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2015</v>
       </c>
@@ -3139,8 +4414,12 @@
       <c r="M6">
         <v>100</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N6">
+        <f t="shared" si="0"/>
+        <v>877</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2016</v>
       </c>
@@ -3180,8 +4459,12 @@
       <c r="M7">
         <v>87</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N7">
+        <f t="shared" si="0"/>
+        <v>903</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2017</v>
       </c>
@@ -3221,8 +4504,12 @@
       <c r="M8">
         <v>104</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N8">
+        <f t="shared" si="0"/>
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2018</v>
       </c>
@@ -3262,8 +4549,12 @@
       <c r="M9">
         <v>95</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N9">
+        <f t="shared" si="0"/>
+        <v>947</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2019</v>
       </c>
@@ -3303,8 +4594,12 @@
       <c r="M10">
         <v>119</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N10">
+        <f t="shared" si="0"/>
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2020</v>
       </c>
@@ -3344,8 +4639,12 @@
       <c r="M11">
         <v>120</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N11">
+        <f t="shared" si="0"/>
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2021</v>
       </c>
@@ -3384,6 +4683,67 @@
       </c>
       <c r="M12">
         <v>99</v>
+      </c>
+      <c r="N12">
+        <f t="shared" si="0"/>
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13">
+        <f>SUM(B2:B12)</f>
+        <v>1062</v>
+      </c>
+      <c r="C13">
+        <f t="shared" ref="C13:N13" si="1">SUM(C2:C12)</f>
+        <v>922</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="1"/>
+        <v>870</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="1"/>
+        <v>732</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="1"/>
+        <v>749</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="1"/>
+        <v>792</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="1"/>
+        <v>883</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="1"/>
+        <v>846</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="1"/>
+        <v>847</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="1"/>
+        <v>815</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="1"/>
+        <v>958</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="1"/>
+        <v>1004</v>
+      </c>
+      <c r="N13">
+        <f t="shared" si="1"/>
+        <v>10480</v>
       </c>
     </row>
   </sheetData>
@@ -3392,6 +4752,310 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94AE742B-6ADF-44B8-9792-98B0806A200F}">
+  <dimension ref="A1:B36"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>21</v>
+      </c>
+      <c r="B31">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>47</v>
+      </c>
+      <c r="B35">
+        <v>2833</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>19</v>
+      </c>
+      <c r="B36">
+        <v>4138</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B1" xr:uid="{94AE742B-6ADF-44B8-9792-98B0806A200F}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B36">
+      <sortCondition ref="B1"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3308E310-C61C-4A2C-96ED-391E0552076A}">
   <dimension ref="A2:J50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
